--- a/data/trans_dic/P16A12-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,61</t>
+          <t>9,53; 13,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 19,96</t>
+          <t>14,87; 19,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 22,03</t>
+          <t>16,45; 22,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 20,46</t>
+          <t>14,91; 20,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,96</t>
+          <t>11,04; 14,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 20,16</t>
+          <t>15,8; 20,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 21,77</t>
+          <t>16,28; 21,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 22,58</t>
+          <t>18,26; 22,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 13,53</t>
+          <t>10,99; 13,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 19,11</t>
+          <t>15,98; 19,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,89; 21,1</t>
+          <t>16,87; 20,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 20,92</t>
+          <t>17,75; 21,08</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,05</t>
+          <t>2,43; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,47</t>
+          <t>2,77; 4,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,83</t>
+          <t>4,77; 6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,93</t>
+          <t>4,5; 7,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,56</t>
+          <t>1,24; 2,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,96</t>
+          <t>2,23; 4,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,14</t>
+          <t>3,12; 5,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,55</t>
+          <t>2,72; 4,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,08</t>
+          <t>2,0; 3,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,98</t>
+          <t>2,73; 3,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,68</t>
+          <t>4,23; 5,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,06</t>
+          <t>4,08; 5,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,43</t>
+          <t>0,9; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,92</t>
+          <t>1,45; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,82</t>
+          <t>2,29; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,92</t>
+          <t>4,38; 7,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,14</t>
+          <t>0,61; 3,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,35</t>
+          <t>0,63; 3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,28</t>
+          <t>0,94; 3,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,41</t>
+          <t>1,71; 3,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,73</t>
+          <t>1,06; 2,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,57</t>
+          <t>1,36; 3,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,17</t>
+          <t>1,86; 4,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,16</t>
+          <t>3,33; 5,21</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,39</t>
+          <t>4,86; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,26</t>
+          <t>6,44; 8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,35</t>
+          <t>7,5; 9,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,3</t>
+          <t>6,09; 9,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,02</t>
+          <t>5,29; 6,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 8,86</t>
+          <t>6,91; 8,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,73</t>
+          <t>5,67; 7,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,38</t>
+          <t>5,3; 6,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,51</t>
+          <t>7,23; 8,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,79</t>
+          <t>7,5; 8,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,24</t>
+          <t>6,42; 8,17</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101474; 140457</t>
+          <t>98369; 138639</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>142987; 194416</t>
+          <t>144799; 192126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124648; 166157</t>
+          <t>124095; 166561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75851; 105153</t>
+          <t>76631; 104782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>146158; 196744</t>
+          <t>145202; 192282</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>212482; 268852</t>
+          <t>210756; 268400</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>160209; 216499</t>
+          <t>161950; 213151</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>138815; 169843</t>
+          <t>137302; 168545</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>253011; 317521</t>
+          <t>257995; 321433</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>365823; 440992</t>
+          <t>368617; 443021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295393; 369016</t>
+          <t>295046; 365229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>222230; 264829</t>
+          <t>224687; 266937</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41928; 68458</t>
+          <t>41046; 70096</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55013; 87614</t>
+          <t>54306; 85967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100140; 141888</t>
+          <t>99096; 143668</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108573; 181687</t>
+          <t>103014; 181869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19023; 40610</t>
+          <t>19722; 41385</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39641; 69357</t>
+          <t>39087; 70545</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64878; 102219</t>
+          <t>61941; 100843</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59589; 101709</t>
+          <t>60766; 101355</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64356; 101026</t>
+          <t>65742; 101251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101651; 147637</t>
+          <t>101223; 144687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173057; 230882</t>
+          <t>171853; 229870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188288; 274566</t>
+          <t>184566; 270957</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5069; 18922</t>
+          <t>4989; 17782</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7624; 23626</t>
+          <t>6976; 23402</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12551; 31843</t>
+          <t>12529; 34259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27659; 51211</t>
+          <t>28342; 49709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3155; 14974</t>
+          <t>2924; 15359</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2758; 15338</t>
+          <t>2877; 14590</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5066; 18008</t>
+          <t>5175; 18678</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10893; 22552</t>
+          <t>11309; 22758</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10971; 28022</t>
+          <t>10907; 28786</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12865; 33504</t>
+          <t>12784; 32207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21156; 45684</t>
+          <t>20415; 44630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42398; 67421</t>
+          <t>43461; 68122</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>158970; 209442</t>
+          <t>159289; 209717</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>218978; 282016</t>
+          <t>220005; 281813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251885; 315788</t>
+          <t>253276; 316025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221870; 321025</t>
+          <t>210318; 315810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>177613; 237097</t>
+          <t>178922; 234057</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>267696; 336316</t>
+          <t>268028; 336282</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>247113; 312817</t>
+          <t>244182; 312453</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>207261; 282209</t>
+          <t>206834; 284563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349023; 424353</t>
+          <t>352733; 426803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>502580; 592217</t>
+          <t>503344; 591124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513543; 607075</t>
+          <t>517992; 609253</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>464865; 584862</t>
+          <t>455554; 580403</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A12-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,44</t>
+          <t>9,69; 13,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,73</t>
+          <t>14,57; 19,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 22,08</t>
+          <t>16,52; 22,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,39</t>
+          <t>14,34; 19,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,62</t>
+          <t>11,04; 14,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,13</t>
+          <t>15,88; 19,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,43</t>
+          <t>16,29; 21,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,41</t>
+          <t>17,96; 22,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,7</t>
+          <t>11,08; 13,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,98; 19,2</t>
+          <t>16,07; 19,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,87; 20,88</t>
+          <t>16,92; 20,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,75; 21,08</t>
+          <t>17,07; 20,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,14</t>
+          <t>2,43; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,39</t>
+          <t>2,82; 4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,92</t>
+          <t>4,79; 6,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,94</t>
+          <t>6,44; 8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,61</t>
+          <t>1,23; 2,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,03</t>
+          <t>2,23; 3,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,07</t>
+          <t>3,16; 5,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,53</t>
+          <t>3,71; 4,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,09</t>
+          <t>2,09; 3,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,9</t>
+          <t>2,78; 3,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,66</t>
+          <t>4,28; 5,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,98</t>
+          <t>5,37; 6,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,22</t>
+          <t>0,95; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,87</t>
+          <t>1,62; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,26</t>
+          <t>2,34; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,69</t>
+          <t>4,53; 8,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,22</t>
+          <t>0,67; 3,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,19</t>
+          <t>0,64; 3,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,4</t>
+          <t>0,92; 3,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,45</t>
+          <t>1,75; 3,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,8</t>
+          <t>0,99; 2,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,43</t>
+          <t>1,31; 3,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,07</t>
+          <t>1,9; 4,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,21</t>
+          <t>3,38; 5,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,4</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,25</t>
+          <t>6,39; 8,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 9,36</t>
+          <t>7,52; 9,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,15</t>
+          <t>7,85; 9,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,93</t>
+          <t>5,24; 6,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,49</t>
+          <t>7,52; 9,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,85</t>
+          <t>6,95; 8,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,8</t>
+          <t>6,85; 8,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,41</t>
+          <t>5,3; 6,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,5</t>
+          <t>7,28; 8,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,82</t>
+          <t>7,49; 8,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,17</t>
+          <t>7,54; 8,57</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90663</t>
+          <t>96667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>164876</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>243631</t>
+          <t>261543</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98369; 138639</t>
+          <t>99971; 137841</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144799; 192126</t>
+          <t>141856; 193927</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124095; 166561</t>
+          <t>124639; 166102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76631; 104782</t>
+          <t>82810; 111956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145202; 192282</t>
+          <t>145241; 193511</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210756; 268400</t>
+          <t>211703; 265884</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>161950; 213151</t>
+          <t>161997; 215463</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>137302; 168545</t>
+          <t>147321; 182056</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>257995; 321433</t>
+          <t>260118; 321099</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>368617; 443021</t>
+          <t>370806; 443928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295046; 365229</t>
+          <t>296015; 366524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>224687; 266937</t>
+          <t>238553; 286640</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153186</t>
+          <t>166215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>93009</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>237277</t>
+          <t>259224</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41046; 70096</t>
+          <t>41062; 69736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54306; 85967</t>
+          <t>55178; 89899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99096; 143668</t>
+          <t>99398; 143082</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103014; 181869</t>
+          <t>143643; 190717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19722; 41385</t>
+          <t>19507; 40342</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39087; 70545</t>
+          <t>39019; 68850</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61941; 100843</t>
+          <t>62919; 101797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60766; 101355</t>
+          <t>80610; 108259</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65742; 101251</t>
+          <t>68564; 101961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101223; 144687</t>
+          <t>103014; 146011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171853; 229870</t>
+          <t>173955; 229699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184566; 270957</t>
+          <t>236184; 287412</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53695</t>
+          <t>61358</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4989; 17782</t>
+          <t>5230; 19626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6976; 23402</t>
+          <t>7767; 24632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12529; 34259</t>
+          <t>12799; 34562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28342; 49709</t>
+          <t>32200; 56907</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2924; 15359</t>
+          <t>3193; 14742</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2877; 14590</t>
+          <t>2950; 15582</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5175; 18678</t>
+          <t>5069; 17863</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11309; 22758</t>
+          <t>12835; 26656</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10907; 28786</t>
+          <t>10192; 27411</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12784; 32207</t>
+          <t>12286; 33210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20415; 44630</t>
+          <t>20791; 45778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43461; 68122</t>
+          <t>48959; 75448</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>281476</t>
+          <t>305547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>253127</t>
+          <t>276577</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>534603</t>
+          <t>582125</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>159289; 209717</t>
+          <t>158228; 209691</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220005; 281813</t>
+          <t>218333; 283093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253276; 316025</t>
+          <t>253846; 319248</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>210318; 315810</t>
+          <t>276139; 336721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>178922; 234057</t>
+          <t>177006; 231537</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>268028; 336282</t>
+          <t>266373; 333522</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>244182; 312453</t>
+          <t>245523; 311844</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>206834; 284563</t>
+          <t>255348; 303876</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>352733; 426803</t>
+          <t>352579; 428694</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>503344; 591124</t>
+          <t>506526; 604961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517992; 609253</t>
+          <t>517395; 612275</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>455554; 580403</t>
+          <t>546067; 621196</t>
         </is>
       </c>
     </row>
